--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -847,13 +847,316 @@
   <si>
     <t>Grand parent Maternel du PEPE</t>
   </si>
+  <si>
+    <t>Marc Antoine Abel</t>
+  </si>
+  <si>
+    <t>1882</t>
+  </si>
+  <si>
+    <t>1913</t>
+  </si>
+  <si>
+    <t>1892</t>
+  </si>
+  <si>
+    <t>1920</t>
+  </si>
+  <si>
+    <t>en 1892</t>
+  </si>
+  <si>
+    <t>en 1882</t>
+  </si>
+  <si>
+    <t>en 1920</t>
+  </si>
+  <si>
+    <t>en 1913</t>
+  </si>
+  <si>
+    <t>1930</t>
+  </si>
+  <si>
+    <t>1927</t>
+  </si>
+  <si>
+    <t>en 1914</t>
+  </si>
+  <si>
+    <t>en 1963</t>
+  </si>
+  <si>
+    <t>P037</t>
+  </si>
+  <si>
+    <t>CRESPY</t>
+  </si>
+  <si>
+    <t>1971</t>
+  </si>
+  <si>
+    <t>P038</t>
+  </si>
+  <si>
+    <t>Louis Henri</t>
+  </si>
+  <si>
+    <t>en 1930</t>
+  </si>
+  <si>
+    <t>en 1927</t>
+  </si>
+  <si>
+    <t>en 1972</t>
+  </si>
+  <si>
+    <t>Louis Henry</t>
+  </si>
+  <si>
+    <t>supposition mari de Marie BERTHOLON (cimetière de Recharinge)</t>
+  </si>
+  <si>
+    <t>supposition marié avec Louis Henri CRESPY (cimetière Recharinge)</t>
+  </si>
+  <si>
+    <t>en 1988</t>
+  </si>
+  <si>
+    <t>Rosalie</t>
+  </si>
+  <si>
+    <t>P039</t>
+  </si>
+  <si>
+    <t>P038;P036</t>
+  </si>
+  <si>
+    <t>P039;P036</t>
+  </si>
+  <si>
+    <t>P038w;P039</t>
+  </si>
+  <si>
+    <t>P038;P039</t>
+  </si>
+  <si>
+    <t>photo fraterie Elise</t>
+  </si>
+  <si>
+    <t>P040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph  </t>
+  </si>
+  <si>
+    <t>photo avec grand père BERTHOLON</t>
+  </si>
+  <si>
+    <t>P041</t>
+  </si>
+  <si>
+    <t>photo avec grand père BERTHOLON (appelé l'oncle)</t>
+  </si>
+  <si>
+    <t>photo avec grand père BERTHOLON (appelé tante)</t>
+  </si>
+  <si>
+    <t>photo avec grand père BERTHOLON (appelé tante); est ce la meme que P025?</t>
+  </si>
+  <si>
+    <t>P042</t>
+  </si>
+  <si>
+    <t>photo avec grand père BERTHOLON (appelé papa); est ce le PEPE</t>
+  </si>
+  <si>
+    <t>P043</t>
+  </si>
+  <si>
+    <t>photo avec grand père BERTHOLON (appelé tante NINI); est ce le PEPE</t>
+  </si>
+  <si>
+    <t>P044</t>
+  </si>
+  <si>
+    <t>Alban</t>
+  </si>
+  <si>
+    <t>photo avec grand père BERTHOLON (appelé oncle Alban); est ce P033?</t>
+  </si>
+  <si>
+    <t>photo à Recharinge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">si grand parent=Cyprien et Elise (P020 et P021) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">photo avec grand père BERTHOLON (appelé tante NINI); est ce </t>
+  </si>
+  <si>
+    <t>si grand parent=Cyprien et Elise (P020 et P021), alors NIN est leur fille qui est marié avec Henri CRESPY</t>
+  </si>
+  <si>
+    <t>si grand parent=Cyprien et Elise (P020 et P021), alors NIN est leur fille qui est marié avec Henri CRESPY, ils ont eu un fils Gérard qui à eu un fils</t>
+  </si>
+  <si>
+    <t>photo vivaquatre 1951</t>
+  </si>
+  <si>
+    <t>arrière grand parent BERTHOLON, grand parents, avec Lisette et leurs garçon</t>
+  </si>
+  <si>
+    <t>arrière grand parent BERTHOLON, grand parents, avec Lisette et leurs garçons: si Lisette (P012) donc garçon (Christian est Hervé) et Lisette aurait sur la photo que 16 ans???</t>
+  </si>
+  <si>
+    <t>photo grand parents BERTHO</t>
+  </si>
+  <si>
+    <t>si grand parent=Cyprien et Elise (P020 et P021), peut etre que NINI est leur fille qui est marié mais ce coup-ci avec Lucien et pas Henri CRESPY,leurs fils Gérard</t>
+  </si>
+  <si>
+    <t>photo à Unias</t>
+  </si>
+  <si>
+    <t>Pierrot BERTHOLON avec les grand parents (si grd parent P020 et P021et que ce Pierrot est leur fils alors Pierrot = P003</t>
+  </si>
+  <si>
+    <t>Portrait de ALAIN BERTHOLON ???</t>
+  </si>
+  <si>
+    <t>P050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alain </t>
+  </si>
+  <si>
+    <t>Portrait de ALAIN BERTHOLON (un frère du PEPE ???)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photo de tante Marie avec Joseph </t>
+  </si>
+  <si>
+    <t>photo de tante Marie avec Joseph (est ce P040 et P041??)</t>
+  </si>
+  <si>
+    <t>photo avec grand père BERTHOLON (appelé tante NINI);</t>
+  </si>
+  <si>
+    <t>si grand parent=Cyprien et Elise (P020 et P021), alors NINI est leur fille qui est marié avec Henri CRESPY, ils ont eu un fils Gérard qui à eu un fils</t>
+  </si>
+  <si>
+    <t>PERRET</t>
+  </si>
+  <si>
+    <t>PAILLEUX</t>
+  </si>
+  <si>
+    <t>CROZIER</t>
+  </si>
+  <si>
+    <t>AUDOUARD</t>
+  </si>
+  <si>
+    <t>P003;P031;P032;P033</t>
+  </si>
+  <si>
+    <t>https://i.postimg.cc/VNVD72C0/pierre-Bertholon.png</t>
+  </si>
+  <si>
+    <t>P004</t>
+  </si>
+  <si>
+    <t>P005</t>
+  </si>
+  <si>
+    <t>P006</t>
+  </si>
+  <si>
+    <t>P003;P004;P005;P006</t>
+  </si>
+  <si>
+    <t>P002;P004;P005;P006</t>
+  </si>
+  <si>
+    <t>P002;P003;P005;P006</t>
+  </si>
+  <si>
+    <t>P002;P003;P004;P006</t>
+  </si>
+  <si>
+    <t>P002;P003;P004;P005</t>
+  </si>
+  <si>
+    <t>P007</t>
+  </si>
+  <si>
+    <t>Victoria</t>
+  </si>
+  <si>
+    <t>JACQUEMETTON</t>
+  </si>
+  <si>
+    <t>P008</t>
+  </si>
+  <si>
+    <t>Gaby</t>
+  </si>
+  <si>
+    <t>BERNARD</t>
+  </si>
+  <si>
+    <t>P001;P008</t>
+  </si>
+  <si>
+    <t>P001;P007</t>
+  </si>
+  <si>
+    <t>fraterie MEME</t>
+  </si>
+  <si>
+    <t>Ginette</t>
+  </si>
+  <si>
+    <t>P051</t>
+  </si>
+  <si>
+    <t>P052</t>
+  </si>
+  <si>
+    <t>P007;P008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">si grand parent=Cyprien et Elise (P020 et P021), alors NINI est leur fille qui est marié avec Henri CRESPY, ils ont eu un fils Gérard </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gérard  </t>
+  </si>
+  <si>
+    <t>P001;P002;</t>
+  </si>
+  <si>
+    <t>P001;P002;P012;P013;P014;P015;P016</t>
+  </si>
+  <si>
+    <t>P001;P002;P012;P013;P014;P015;P016;P017;P018;P019</t>
+  </si>
+  <si>
+    <t>P001;P002;P012;P013;P014;P015;P016;P017;P018;P019;P010;P011;P020;P021</t>
+  </si>
+  <si>
+    <t>P005;P020;P021</t>
+  </si>
+  <si>
+    <t>P021;P004;P003</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -913,8 +1216,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -957,6 +1282,43 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BBB59"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAC090"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCD5B5"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -970,7 +1332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1045,6 +1407,86 @@
     <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="7" applyFill="1" applyAlignment="1" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="8" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="8" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="8" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="8" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="9" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="10" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="3" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="8" applyFont="1" fillId="3" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="8" applyFont="1" fillId="7" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="6" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="5" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="11" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="11" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="11" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="11" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="12" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="12" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="12" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="12" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="3" applyFont="1" fillId="11" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="8" applyFont="1" fillId="11" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="13" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="13" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="3" applyFont="1" fillId="13" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="8" applyFont="1" fillId="13" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="14" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="14" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="14" applyFill="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1534,7 +1976,7 @@
     <col width="30.7265625" customWidth="1" min="14" max="14" bestFit="1"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="76.6328125" customWidth="1" min="16" max="16" bestFit="1"/>
-    <col width="43.26953125" customWidth="1" min="17" max="17" bestFit="1"/>
+    <col width="44.453125" customWidth="1" min="17" max="17" bestFit="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" ht="33.75">
@@ -1590,905 +2032,927 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
+    <row r="2" customFormat="1" s="17">
+      <c r="A2" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4" t="s">
+      <c r="L2" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="M2" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="3" t="s">
+      <c r="P2" s="18"/>
+      <c r="Q2" s="41" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
+    <row r="3" customFormat="1" s="17">
+      <c r="A3" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="18" t="s">
+        <v>352</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="41" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" s="13">
+      <c r="A4" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="O3" s="4" t="s">
+      <c r="B4" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="15"/>
+      <c r="I4" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="M4" s="14">
+        <v>1</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="O4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="P4" s="14"/>
+      <c r="Q4" s="42" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" s="13">
+      <c r="A5" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4" t="s">
+      <c r="E5" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="M5" s="14">
+        <v>1</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q5" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" s="13">
+      <c r="A6" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="F6" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="4" t="s">
+      <c r="H6" s="15"/>
+      <c r="I6" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J6" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="M4" s="4">
+      <c r="K6" s="14"/>
+      <c r="L6" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="M6" s="14">
         <v>1</v>
       </c>
-      <c r="N4" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="O4" s="4" t="s">
+      <c r="N6" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" s="13">
+      <c r="A7" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="M7" s="14">
+        <v>1</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" s="47">
+      <c r="A8" s="48" t="s">
+        <v>357</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>358</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>359</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="49"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48" t="s">
+        <v>363</v>
+      </c>
+      <c r="M8" s="48">
+        <v>1</v>
+      </c>
+      <c r="N8" s="48" t="s">
+        <v>365</v>
+      </c>
+      <c r="O8" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
+      <c r="P8" s="48"/>
+      <c r="Q8" s="50"/>
+    </row>
+    <row r="9" customFormat="1" s="47">
+      <c r="A9" s="48" t="s">
+        <v>360</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>361</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>362</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="49"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4" t="s">
+      <c r="J9" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4">
-        <v>2</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4">
-        <v>2</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="M7" s="4">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="M8" s="4">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="M9" s="4">
-        <v>0</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="6" t="s">
-        <v>63</v>
-      </c>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48" t="s">
+        <v>364</v>
+      </c>
+      <c r="M9" s="48">
+        <v>1</v>
+      </c>
+      <c r="N9" s="48" t="s">
+        <v>365</v>
+      </c>
+      <c r="O9" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="50"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>173</v>
+        <v>58</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>175</v>
-      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
       <c r="H10" s="5"/>
-      <c r="I10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4" t="s">
-        <v>187</v>
-      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="4"/>
       <c r="M10" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>249</v>
+        <v>193</v>
       </c>
       <c r="O10" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P10" s="4"/>
-      <c r="Q10" s="6" t="s">
+      <c r="Q10" s="4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>176</v>
+        <v>60</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="E11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>175</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4" t="s">
-        <v>188</v>
-      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="4"/>
       <c r="M11" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>249</v>
+        <v>193</v>
       </c>
       <c r="O11" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P11" s="4"/>
-      <c r="Q11" s="6" t="s">
-        <v>57</v>
+      <c r="Q11" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>161</v>
+        <v>46</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>178</v>
+        <v>68</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>179</v>
+        <v>69</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4" t="s">
-        <v>189</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>292</v>
+      </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12" s="4"/>
       <c r="M12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>249</v>
+        <v>194</v>
       </c>
       <c r="O12" s="4" t="s">
         <v>40</v>
       </c>
       <c r="P12" s="4"/>
-      <c r="Q12" s="6" t="s">
+      <c r="Q12" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" s="53">
+      <c r="A13" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="I13" s="54" t="s">
+        <v>265</v>
+      </c>
+      <c r="J13" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="K13" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13" s="54"/>
+      <c r="M13" s="54">
+        <v>2</v>
+      </c>
+      <c r="N13" s="54" t="s">
+        <v>194</v>
+      </c>
+      <c r="O13" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="P13" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q13" s="54" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
+    <row r="14" customFormat="1" s="32">
+      <c r="A14" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>343</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="34"/>
+      <c r="I14" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="M14" s="33">
+        <v>0</v>
+      </c>
+      <c r="N14" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="O14" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="35" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" s="32">
+      <c r="A15" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>253</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>344</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="H15" s="34"/>
+      <c r="I15" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="M15" s="33">
+        <v>0</v>
+      </c>
+      <c r="N15" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="O15" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="35" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" s="32">
+      <c r="A16" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>345</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="H16" s="34"/>
+      <c r="I16" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="M16" s="33">
+        <v>0</v>
+      </c>
+      <c r="N16" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="O16" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="35" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" s="32">
+      <c r="A17" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" s="34"/>
+      <c r="I17" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="M17" s="33">
+        <v>0</v>
+      </c>
+      <c r="N17" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="O17" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="35" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" s="32">
+      <c r="A18" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="H18" s="34"/>
+      <c r="I18" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="M18" s="33">
+        <v>0</v>
+      </c>
+      <c r="N18" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="O18" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="35" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" s="32">
+      <c r="A19" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>346</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="H19" s="34"/>
+      <c r="I19" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="J19" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="M19" s="33">
+        <v>0</v>
+      </c>
+      <c r="N19" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="O19" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="35" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" s="32">
+      <c r="A20" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="B20" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="C20" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
+      <c r="D20" s="33"/>
+      <c r="E20" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F20" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G20" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="4" t="s">
+      <c r="H20" s="34"/>
+      <c r="I20" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J20" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4" t="s">
+      <c r="K20" s="33"/>
+      <c r="L20" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="M13" s="4">
+      <c r="M20" s="33">
         <v>0</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="N20" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="O20" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="6" t="s">
+      <c r="P20" s="33"/>
+      <c r="Q20" s="35" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="s">
+    <row r="21" customFormat="1" s="32">
+      <c r="A21" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B21" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C21" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4" t="s">
+      <c r="D21" s="33"/>
+      <c r="E21" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F21" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G21" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="4" t="s">
+      <c r="H21" s="34"/>
+      <c r="I21" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J21" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4" t="s">
+      <c r="K21" s="33"/>
+      <c r="L21" s="33" t="s">
         <v>191</v>
       </c>
-      <c r="M14" s="4">
+      <c r="M21" s="33">
         <v>0</v>
       </c>
-      <c r="N14" s="4" t="s">
+      <c r="N21" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="O21" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4">
-        <v>2</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" s="26">
-      <c r="A16" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="28"/>
-      <c r="I16" s="27" t="s">
-        <v>265</v>
-      </c>
-      <c r="J16" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="K16" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27">
-        <v>2</v>
-      </c>
-      <c r="N16" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="O16" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="P16" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q16" s="27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" s="9">
-      <c r="A17" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M17" s="10">
-        <v>2</v>
-      </c>
-      <c r="N17" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="O17" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="P17" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q17" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" s="9">
-      <c r="A18" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="M18" s="10">
-        <v>2</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="O18" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="P18" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q18" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" s="9">
-      <c r="A19" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="M19" s="10">
-        <v>2</v>
-      </c>
-      <c r="N19" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="O19" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q19" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" s="9">
-      <c r="A20" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="M20" s="10">
-        <v>2</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="O20" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="P20" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q20" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" s="9">
-      <c r="A21" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="M21" s="10">
-        <v>2</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="O21" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="P21" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q21" s="12" t="s">
+      <c r="P21" s="33"/>
+      <c r="Q21" s="35" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="22" customFormat="1" s="9">
       <c r="A22" s="10" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="D22" s="10" t="s">
         <v>65</v>
       </c>
+      <c r="D22" s="10"/>
       <c r="E22" s="10" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F22" s="11"/>
       <c r="G22" s="10"/>
@@ -2499,34 +2963,32 @@
       <c r="J22" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="K22" s="10" t="s">
-        <v>248</v>
-      </c>
+      <c r="K22" s="10"/>
       <c r="L22" s="10" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="M22" s="10">
         <v>2</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="O22" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P22" s="10" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" customFormat="1" s="9">
       <c r="A23" s="10" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>65</v>
@@ -2537,9 +2999,7 @@
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="11" t="s">
-        <v>208</v>
-      </c>
+      <c r="H23" s="11"/>
       <c r="I23" s="10" t="s">
         <v>73</v>
       </c>
@@ -2548,7 +3008,7 @@
       </c>
       <c r="K23" s="10"/>
       <c r="L23" s="10" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="M23" s="10">
         <v>2</v>
@@ -2560,460 +3020,600 @@
         <v>55</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="Q23" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" customFormat="1" s="13">
-      <c r="A24" s="14" t="s">
+    <row r="24" customFormat="1" s="9">
+      <c r="A24" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="I24" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="J24" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="M24" s="10">
+        <v>2</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="O24" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P24" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q24" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" s="9">
+      <c r="A25" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="G25" s="10"/>
+      <c r="H25" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="M25" s="10">
+        <v>2</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="O25" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P25" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q25" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" s="9">
+      <c r="A26" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="11"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="M26" s="10">
+        <v>2</v>
+      </c>
+      <c r="N26" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="O26" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P26" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q26" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" s="9">
+      <c r="A27" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="11"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="M27" s="10">
+        <v>2</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="O27" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P27" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q27" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" s="9">
+      <c r="A28" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="11"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M28" s="10">
+        <v>2</v>
+      </c>
+      <c r="N28" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="O28" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P28" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q28" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" s="13">
+      <c r="A29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C29" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14" t="s">
+      <c r="D29" s="14"/>
+      <c r="E29" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="15" t="s">
+      <c r="F29" s="15"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14" t="s">
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14">
+      <c r="L29" s="14"/>
+      <c r="M29" s="14">
         <v>3</v>
       </c>
-      <c r="N24" s="14" t="s">
+      <c r="N29" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="O24" s="14" t="s">
+      <c r="O29" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="16" t="s">
+      <c r="P29" s="14"/>
+      <c r="Q29" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25" customFormat="1" s="13">
-      <c r="A25" s="14" t="s">
+    <row r="30" customFormat="1" s="13">
+      <c r="A30" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B30" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C30" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14" t="s">
+      <c r="D30" s="14"/>
+      <c r="E30" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="15" t="s">
+      <c r="F30" s="15"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14" t="s">
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14">
+      <c r="L30" s="14"/>
+      <c r="M30" s="14">
         <v>3</v>
       </c>
-      <c r="N25" s="14" t="s">
+      <c r="N30" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="O25" s="14" t="s">
+      <c r="O30" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="16" t="s">
+      <c r="P30" s="14"/>
+      <c r="Q30" s="16" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4" t="s">
+    <row r="31">
+      <c r="A31" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4">
+        <v>2</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" s="29">
+      <c r="A32" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="F32" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="G32" s="30"/>
+      <c r="H32" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="L32" s="30" t="s">
+        <v>309</v>
+      </c>
+      <c r="M32" s="30">
+        <v>3</v>
+      </c>
+      <c r="N32" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="O32" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" s="29">
+      <c r="A33" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="E33" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M26" s="4">
-        <v>1</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="O26" s="4" t="s">
+      <c r="F33" s="31" t="s">
+        <v>271</v>
+      </c>
+      <c r="G33" s="30"/>
+      <c r="H33" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="L33" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="M33" s="30">
+        <v>3</v>
+      </c>
+      <c r="N33" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="O33" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="6" t="s">
+      <c r="P33" s="30" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q33" s="27" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4" t="s">
+    <row r="34">
+      <c r="A34" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="5"/>
-      <c r="I27" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="M27" s="4">
-        <v>1</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="O27" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="M28" s="4">
-        <v>1</v>
-      </c>
-      <c r="N28" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="O28" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4">
-        <v>2</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" s="29">
-      <c r="A30" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>266</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="G30" s="30"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30">
-        <v>3</v>
-      </c>
-      <c r="N30" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="O30" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="P30" s="30"/>
-      <c r="Q30" s="27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" s="29">
-      <c r="A31" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C31" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="G31" s="30"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30">
-        <v>3</v>
-      </c>
-      <c r="N31" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="O31" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="5"/>
+      <c r="F34" s="5" t="s">
+        <v>285</v>
+      </c>
       <c r="G34" s="4"/>
-      <c r="H34" s="5"/>
+      <c r="H34" s="5" t="s">
+        <v>297</v>
+      </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
+      <c r="K34" s="4" t="s">
+        <v>349</v>
+      </c>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
+      <c r="O34" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q34" s="6" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
+      <c r="A35" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F35" s="5"/>
       <c r="G35" s="4"/>
       <c r="H35" s="5"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
+      <c r="L35" s="4" t="s">
+        <v>305</v>
+      </c>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
+      <c r="O35" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>308</v>
+      </c>
       <c r="Q35" s="4"/>
     </row>
     <row r="36">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
+      <c r="A36" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F36" s="5"/>
       <c r="G36" s="4"/>
       <c r="H36" s="5"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
+      <c r="L36" s="4" t="s">
+        <v>304</v>
+      </c>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
+      <c r="O36" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>308</v>
+      </c>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
+    <row r="37" customFormat="1" s="58">
+      <c r="A37" s="59" t="s">
+        <v>309</v>
+      </c>
+      <c r="B37" s="59" t="s">
+        <v>310</v>
+      </c>
+      <c r="C37" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="60"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="59"/>
+      <c r="K37" s="59"/>
+      <c r="L37" s="59"/>
+      <c r="M37" s="59"/>
+      <c r="N37" s="59"/>
+      <c r="O37" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="P37" s="59" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q37" s="59"/>
     </row>
     <row r="38">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
+      <c r="A38" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
+      <c r="E38" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F38" s="5"/>
       <c r="G38" s="4"/>
       <c r="H38" s="5"/>
@@ -3023,35 +3623,59 @@
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
+      <c r="O38" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>315</v>
+      </c>
       <c r="Q38" s="4"/>
     </row>
     <row r="39">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
+      <c r="A39" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>291</v>
+      </c>
       <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
+      <c r="E39" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="F39" s="5"/>
       <c r="G39" s="4"/>
       <c r="H39" s="5"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
+      <c r="I39" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>349</v>
+      </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
+      <c r="O39" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>317</v>
+      </c>
       <c r="Q39" s="4"/>
     </row>
     <row r="40">
-      <c r="A40" s="4"/>
+      <c r="A40" s="4" t="s">
+        <v>318</v>
+      </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
+      <c r="E40" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F40" s="5"/>
       <c r="G40" s="4"/>
       <c r="H40" s="5"/>
@@ -3061,8 +3685,12 @@
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
+      <c r="O40" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>341</v>
+      </c>
       <c r="Q40" s="4"/>
     </row>
     <row r="41">
@@ -3081,7 +3709,9 @@
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
+      <c r="P41" s="10" t="s">
+        <v>323</v>
+      </c>
       <c r="Q41" s="4"/>
     </row>
     <row r="42">
@@ -3100,7 +3730,9 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
+      <c r="P42" s="10" t="s">
+        <v>370</v>
+      </c>
       <c r="Q42" s="4"/>
     </row>
     <row r="43">
@@ -3119,7 +3751,9 @@
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
+      <c r="P43" s="36" t="s">
+        <v>328</v>
+      </c>
       <c r="Q43" s="4"/>
     </row>
     <row r="44">
@@ -3138,7 +3772,9 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
+      <c r="P44" s="36" t="s">
+        <v>330</v>
+      </c>
       <c r="Q44" s="4"/>
     </row>
     <row r="45">
@@ -3157,7 +3793,9 @@
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
+      <c r="P45" s="37" t="s">
+        <v>331</v>
+      </c>
       <c r="Q45" s="4"/>
     </row>
     <row r="46">
@@ -3176,7 +3814,9 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
+      <c r="P46" s="37" t="s">
+        <v>332</v>
+      </c>
       <c r="Q46" s="4"/>
     </row>
     <row r="47">
@@ -3195,7 +3835,9 @@
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
+      <c r="P47" s="38" t="s">
+        <v>333</v>
+      </c>
       <c r="Q47" s="4"/>
     </row>
     <row r="48">
@@ -3214,53 +3856,95 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
+      <c r="P48" s="38" t="s">
+        <v>334</v>
+      </c>
       <c r="Q48" s="4"/>
     </row>
     <row r="49">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
+      <c r="A49" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
+      <c r="E49" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="F49" s="5"/>
       <c r="G49" s="4"/>
       <c r="H49" s="5"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
+      <c r="I49" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>368</v>
+      </c>
       <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
+      <c r="L49" s="4" t="s">
+        <v>367</v>
+      </c>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
+      <c r="P49" s="4" t="s">
+        <v>338</v>
+      </c>
       <c r="Q49" s="4"/>
     </row>
     <row r="50">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
+      <c r="A50" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
+      <c r="E50" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="F50" s="5"/>
       <c r="G50" s="4"/>
       <c r="H50" s="5"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
+      <c r="I50" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>368</v>
+      </c>
       <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
+      <c r="L50" s="4" t="s">
+        <v>368</v>
+      </c>
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
+      <c r="P50" s="4" t="s">
+        <v>340</v>
+      </c>
       <c r="Q50" s="4"/>
     </row>
     <row r="51">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
+      <c r="A51" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
+      <c r="E51" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="F51" s="5"/>
       <c r="G51" s="4"/>
       <c r="H51" s="5"/>
@@ -7303,8 +7987,23 @@
       <c r="Q263" s="4"/>
     </row>
     <row r="264">
-      <c r="F264" s="2"/>
-      <c r="H264" s="2"/>
+      <c r="A264" s="4"/>
+      <c r="B264" s="4"/>
+      <c r="C264" s="4"/>
+      <c r="D264" s="4"/>
+      <c r="E264" s="4"/>
+      <c r="F264" s="5"/>
+      <c r="G264" s="4"/>
+      <c r="H264" s="5"/>
+      <c r="I264" s="4"/>
+      <c r="J264" s="4"/>
+      <c r="K264" s="4"/>
+      <c r="L264" s="4"/>
+      <c r="M264" s="4"/>
+      <c r="N264" s="4"/>
+      <c r="O264" s="4"/>
+      <c r="P264" s="4"/>
+      <c r="Q264" s="4"/>
     </row>
     <row r="265">
       <c r="F265" s="2"/>
@@ -8245,6 +8944,10 @@
     <row r="499">
       <c r="F499" s="2"/>
       <c r="H499" s="2"/>
+    </row>
+    <row r="500">
+      <c r="F500" s="2"/>
+      <c r="H500" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8295,8 +8998,8 @@
       <c r="C2" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D2" t="s">
-        <v>195</v>
+      <c r="D2" s="63" t="s">
+        <v>375</v>
       </c>
       <c r="E2" t="s">
         <v>198</v>
@@ -8381,7 +9084,7 @@
         <v>210</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>350</v>
       </c>
       <c r="E7" t="s">
         <v>197</v>
@@ -8415,7 +9118,7 @@
         <v>214</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>351</v>
       </c>
       <c r="E9" t="s">
         <v>197</v>
@@ -8432,7 +9135,7 @@
         <v>217</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>351</v>
       </c>
       <c r="E10" t="s">
         <v>197</v>
@@ -8466,7 +9169,7 @@
         <v>220</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>350</v>
       </c>
       <c r="E12" t="s">
         <v>197</v>
@@ -8534,7 +9237,7 @@
         <v>237</v>
       </c>
       <c r="D16" t="s">
-        <v>238</v>
+        <v>376</v>
       </c>
       <c r="E16" t="s">
         <v>197</v>
@@ -8568,7 +9271,7 @@
         <v>242</v>
       </c>
       <c r="D18" t="s">
-        <v>245</v>
+        <v>377</v>
       </c>
       <c r="E18" t="s">
         <v>197</v>

--- a/data/Genealogie_MEME.xlsx
+++ b/data/Genealogie_MEME.xlsx
@@ -3460,145 +3460,145 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="s">
+    <row r="34" customFormat="1" s="13">
+      <c r="A34" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4" t="s">
+      <c r="D34" s="14"/>
+      <c r="E34" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="5" t="s">
+      <c r="G34" s="14"/>
+      <c r="H34" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4" t="s">
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4" t="s">
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="P34" s="4" t="s">
+      <c r="P34" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="Q34" s="6" t="s">
+      <c r="Q34" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="s">
+    <row r="35" customFormat="1" s="58">
+      <c r="A35" s="59" t="s">
         <v>293</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="59" t="s">
         <v>302</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="59" t="s">
         <v>270</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="59" t="s">
         <v>270</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="F35" s="5"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4" t="s">
+      <c r="F35" s="60"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
+      <c r="L35" s="59" t="s">
         <v>305</v>
       </c>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4" t="s">
+      <c r="M35" s="59"/>
+      <c r="N35" s="59"/>
+      <c r="O35" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="P35" s="4" t="s">
+      <c r="P35" s="59" t="s">
         <v>308</v>
       </c>
-      <c r="Q35" s="4"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="s">
+      <c r="Q35" s="59"/>
+    </row>
+    <row r="36" customFormat="1" s="58">
+      <c r="A36" s="59" t="s">
         <v>303</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="59" t="s">
         <v>270</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="59" t="s">
         <v>270</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4" t="s">
+      <c r="F36" s="60"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="59"/>
+      <c r="J36" s="59"/>
+      <c r="K36" s="59"/>
+      <c r="L36" s="59" t="s">
         <v>304</v>
       </c>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4" t="s">
+      <c r="M36" s="59"/>
+      <c r="N36" s="59"/>
+      <c r="O36" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="P36" s="4" t="s">
+      <c r="P36" s="59" t="s">
         <v>308</v>
       </c>
-      <c r="Q36" s="4"/>
-    </row>
-    <row r="37" customFormat="1" s="58">
-      <c r="A37" s="59" t="s">
+      <c r="Q36" s="59"/>
+    </row>
+    <row r="37" customFormat="1" s="43">
+      <c r="A37" s="44" t="s">
         <v>309</v>
       </c>
-      <c r="B37" s="59" t="s">
+      <c r="B37" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="C37" s="59" t="s">
+      <c r="C37" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="D37" s="59"/>
-      <c r="E37" s="59" t="s">
+      <c r="D37" s="44"/>
+      <c r="E37" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F37" s="60"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="60"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="59"/>
-      <c r="K37" s="59"/>
-      <c r="L37" s="59"/>
-      <c r="M37" s="59"/>
-      <c r="N37" s="59"/>
-      <c r="O37" s="59" t="s">
+      <c r="F37" s="45"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="44"/>
+      <c r="L37" s="44"/>
+      <c r="M37" s="44"/>
+      <c r="N37" s="44"/>
+      <c r="O37" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="P37" s="59" t="s">
+      <c r="P37" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="Q37" s="59"/>
+      <c r="Q37" s="44"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
